--- a/output/pdf_financials_xlsx/DCY.xlsx
+++ b/output/pdf_financials_xlsx/DCY.xlsx
@@ -5765,37 +5765,37 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.334174</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.419595</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.484392</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.484392</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.127494</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.053844</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="O92" s="3" t="n">
         <v>0</v>
@@ -10252,7 +10252,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10518,7 +10522,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -11850,7 +11858,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DCY.xlsx
+++ b/output/pdf_financials_xlsx/DCY.xlsx
@@ -1096,49 +1096,49 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000732</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000787</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.003522</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002218</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000656</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.000253</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001003</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000156</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000234</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000208</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>4.1e-05</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>3.5e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000276</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000253</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.003628</v>
       </c>
     </row>
     <row r="13">
@@ -2031,49 +2031,49 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.18448</v>
+        <v>-0.185212</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.608165</v>
+        <v>-0.608952</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.497645</v>
+        <v>-0.501167</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.361258</v>
+        <v>-0.363476</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.621646</v>
+        <v>-0.622302</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.226284</v>
+        <v>-0.226537</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.176396</v>
+        <v>-0.177399</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.156249</v>
+        <v>-0.156405</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.129504</v>
+        <v>-0.129738</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.186857</v>
+        <v>-0.187065</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.127175</v>
+        <v>-0.127216</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.212136</v>
+        <v>-0.212171</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.197591</v>
+        <v>-0.197867</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.14964</v>
+        <v>-0.149893</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.625532</v>
+        <v>0.621904</v>
       </c>
     </row>
     <row r="28">
@@ -2145,49 +2145,49 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.18448</v>
+        <v>-0.185212</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.608165</v>
+        <v>-0.608952</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.497645</v>
+        <v>-0.501167</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.361258</v>
+        <v>-0.363476</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.621646</v>
+        <v>-0.622302</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.226284</v>
+        <v>-0.226537</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.176396</v>
+        <v>-0.177399</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.156249</v>
+        <v>-0.156405</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.129504</v>
+        <v>-0.129738</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.186857</v>
+        <v>-0.187065</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.127175</v>
+        <v>-0.127216</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.212136</v>
+        <v>-0.212171</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.197591</v>
+        <v>-0.197867</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.14964</v>
+        <v>-0.149893</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.625532</v>
+        <v>0.621904</v>
       </c>
     </row>
     <row r="30">
@@ -2435,52 +2435,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.100221</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.340216</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.7566659999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.410788</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.148036</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.12976</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.01072</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.054027</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.015729</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.030713</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.19033</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.065195</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.031746</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.040072</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.007204</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.348058</v>
       </c>
     </row>
     <row r="35">
@@ -2545,52 +2545,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.08</v>
+        <v>0.180221</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0175</v>
+        <v>0.357716</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.7566659999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.410788</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.180759</v>
+        <v>0.328795</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.080715</v>
+        <v>0.210475</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.029111</v>
+        <v>0.039831</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.059715</v>
+        <v>0.113742</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.038587</v>
+        <v>0.054316</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.006844</v>
+        <v>0.037557</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.19033</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.065195</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.031746</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.040072</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.007204</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.348058</v>
       </c>
     </row>
     <row r="37">
@@ -3205,52 +3205,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.100221</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.340216</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.750463</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.410788</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.148036</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.12976</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.01072</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.054027</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.015729</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.030713</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.19033</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.065195</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.031746</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.040072</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.007204</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.348058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -18536,7 +18536,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">

--- a/output/pdf_financials_xlsx/DCY.xlsx
+++ b/output/pdf_financials_xlsx/DCY.xlsx
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.001847</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.002421</v>
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.005197</v>
+        <v>0.00335</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.004558</v>
@@ -7031,10 +7031,10 @@
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.082372</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.02445</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7058,7 +7058,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.006844</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -14434,7 +14434,11 @@
           <t>Proceeds from sale of marketable securities 14</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -17186,7 +17190,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -17766,7 +17774,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
